--- a/SampleData/PayData.xlsx
+++ b/SampleData/PayData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/SampleData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1A98EF-2142-C04E-AE0C-16ABDE36CD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAB728D-031E-294B-BCE7-306B9DF63A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{7EE042D0-FE6D-694D-BB75-1F8C0B492E8B}"/>
+    <workbookView xWindow="640" yWindow="500" windowWidth="35840" windowHeight="21100" xr2:uid="{7EE042D0-FE6D-694D-BB75-1F8C0B492E8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
